--- a/backend/tests/fixtures/rate_library_sample.xlsx
+++ b/backend/tests/fixtures/rate_library_sample.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,231 @@
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Margin — Pipe sleeve 110 mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CLIENT D</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>d.xlsx</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>below ₹1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hacking and cleaning of old plaster surface</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sqm</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CLIENT D</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>d.xlsx</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>below ₹1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Crystalline coating to water tank walls with two coats</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sqm</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>150</v>
+      </c>
+      <c r="E9" t="n">
+        <v>150</v>
+      </c>
+      <c r="F9" t="n">
+        <v>150</v>
+      </c>
+      <c r="G9" t="n">
+        <v>150</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CLIENT E</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>e.xlsx</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>comparative sheet (may be other bidders)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Treatment around pipe outlet with polymer modified mortar</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>300</v>
+      </c>
+      <c r="E10" t="n">
+        <v>250</v>
+      </c>
+      <c r="F10" t="n">
+        <v>275</v>
+      </c>
+      <c r="G10" t="n">
+        <v>300</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CLIENT F</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>f.xlsx</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Treatment around pipe outlet with polymer modified mortar</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sqm</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1087</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1087</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1087</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1087</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CLIENT H</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>h.xlsx</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -716,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,6 +1430,314 @@
       <c r="O9" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CLIENT D</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CLIENT D/d.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pipe sleeve 110 mm</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>below ₹1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CLIENT E</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CLIENT E/e.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Comparative</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crystalline coating to water tank walls with two coats</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sqm</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>500</v>
+      </c>
+      <c r="L11" t="n">
+        <v>150</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>comparative sheet (may be other bidders)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CLIENT E</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CLIENT E/e.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Comparative</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Providing and applying APP modified bitumen membrane 4 mm thick over terrace slab</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sqm</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>900</v>
+      </c>
+      <c r="L12" t="n">
+        <v>999</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>comparative sheet (may be other bidders)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CLIENT F</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CLIENT F/f.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BOQ</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Treatment around pipe outlet with polymer modified mortar</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" t="n">
+        <v>300</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CLIENT G</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CLIENT G/g.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BOQ</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Treatment around pipe outlet with polymer modified mortar</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nos</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>250</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CLIENT H</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CLIENT H/h.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BOQ</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Treatment around pipe outlet with polymer modified mortar</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sqm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sqm</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1087</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
